--- a/SQL缺陷分析结果.xlsx
+++ b/SQL缺陷分析结果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Study\LLM\Bug聚类分析\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D57D8AC1-7A17-42C9-A8CB-FE178226DF8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96584ADE-75AB-401B-842E-33C14EF34E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15202,6 +15202,8 @@
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -15557,6 +15559,7 @@
   <dimension ref="A1:S1925"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="22" customWidth="1"/>
     <col min="16" max="16" width="29.875" customWidth="1"/>
     <col min="17" max="17" width="25.375" customWidth="1"/>
